--- a/website/tbls/write_up.xlsx
+++ b/website/tbls/write_up.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="95">
   <si>
     <t xml:space="preserve">section_no</t>
   </si>
@@ -955,7 +955,9 @@
       <c r="B19" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="4"/>
+      <c r="C19" s="4" t="s">
+        <v>72</v>
+      </c>
       <c r="D19" s="4" t="s">
         <v>27</v>
       </c>
@@ -977,7 +979,9 @@
       <c r="B20" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C20" s="4"/>
+      <c r="C20" s="4" t="s">
+        <v>72</v>
+      </c>
       <c r="D20" s="4" t="s">
         <v>76</v>
       </c>
@@ -997,7 +1001,9 @@
       <c r="B21" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="4"/>
+      <c r="C21" s="4" t="s">
+        <v>72</v>
+      </c>
       <c r="D21" s="4" t="s">
         <v>79</v>
       </c>
@@ -1017,7 +1023,9 @@
       <c r="B22" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C22" s="4"/>
+      <c r="C22" s="4" t="s">
+        <v>82</v>
+      </c>
       <c r="D22" s="4" t="s">
         <v>83</v>
       </c>
@@ -1041,7 +1049,9 @@
       <c r="B23" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C23" s="4"/>
+      <c r="C23" s="4" t="s">
+        <v>82</v>
+      </c>
       <c r="D23" s="4" t="s">
         <v>87</v>
       </c>
